--- a/use_cases/2025 DEC 1225 Smoke testing on prod env.xlsx
+++ b/use_cases/2025 DEC 1225 Smoke testing on prod env.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -317,6 +317,42 @@
 3. 3. Checkbox is checked and selection is registered.
 4. 4. Selected poster is added to the ticket product media section.</t>
   </si>
+  <si>
+    <t>T4777</t>
+  </si>
+  <si>
+    <t>Verify when "Enable co-selling by default" is on, create an event post, the resale setting will be turned on</t>
+  </si>
+  <si>
+    <r>
+      <t>1. turn on "Enable co-selling by default" and set the default commission rate
+2. create an event post from: 
+event list,
+event landing page&gt;more action,
+event landing page&gt;Event&gt;Posts&gt;Create a post,
++button&gt;Create a post</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Verdana"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+post module&gt;Add new</t>
+    </r>
+  </si>
+  <si>
+    <t>the resale setting will be turned on and it will use the ticket and merch commission rate</t>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +364,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <name val="Verdana"/>
@@ -484,6 +520,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="33">
@@ -803,7 +844,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1555,7 +1596,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="11" style="1" customWidth="1"/>
@@ -1901,6 +1942,35 @@
       </c>
       <c r="L9" s="1" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="10" ht="306" customHeight="1" spans="1:12">
+      <c r="A10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
